--- a/stories/arbres/ATOM-FAM.AID.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Karim est dans la cuisine. Il veut le bocal de farine. Le bocal est en haut. Trop haut. Karim lève les bras. Il n'arrive pas. Ses épaules se tendent. Karim va vers la porte. Il va vers papa. Papa est dans le salon. Karim dit : papa. J'ai besoin du bocal. Papa écoute. Papa vient. Papa donne le bocal. Le bocal est lourd. Karim dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman arrive aussi. Elle pose un saladier. Karim verse un peu de farine. Un nuage blanc monte. Papa sourit. Parce que Karim a dit le besoin, le bocal est là. Ce n'est pas être petit. C'est demander.</t>
+          <t>Karim est dans la cuisine. Il veut le bocal de farine. Le bocal est en haut. Trop haut. Karim lève les bras. Il n'arrive pas. Ses épaules se tendent. Karim va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin du bocal. Papa écoute. Papa vient. Papa donne le bocal. Le bocal est lourd. Karim dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman arrive aussi. Elle pose un saladier. Karim verse un peu de farine. Un nuage blanc monte. Papa sourit. Parce que Karim a dit le besoin, le bocal est là. Ce n'est pas être petit. C'est demander.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Karim est dans la cuisine. Il veut le bocal de farine. Le bocal est en haut. Trop haut. Karim lève les bras. Il n'arrive pas. Ses épaules se tendent. Karim va vers la porte. Il va vers papa. Papa est dans le salon.
+enfant-m|Papa. J'ai besoin du bocal. Papa écoute. Papa vient. Papa donne le bocal.
+narrateur|Le bocal est lourd. Karim dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman arrive aussi. Elle pose un saladier. Karim verse un peu de farine. Un nuage blanc monte. Papa sourit. Parce que Karim a dit le besoin, le bocal est là. Ce n'est pas être petit. C'est demander.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Karim n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1657,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Karim a appelé. Il a dit le besoin. Papa a entendu. Le bocal est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1820,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Karim mélange la farine. Papa s'assoit près de lui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1987,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2027,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Le bocal est lourd. Karim dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman arrive aussi. Elle pose un saladier. Karim verse un peu de farine. Un nuage blanc monte. Papa sourit. Parce que Karim a dit le besoin, le bocal est là. Ce n'est pas être petit. C'est demander.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Karim n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1662,6 +1673,7 @@
           <t>narrateur|Karim a appelé. Il a dit le besoin. Papa a entendu. Le bocal est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1837,7 @@
           <t>narrateur|Karim mélange la farine. Papa s'assoit près de lui.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1992,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2010,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2034,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2235,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.AID.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Karim appelle papa pour le bocal</t>
+          <t>Le saladier d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le saladier de bois attend près de la vanille. Aniss veut le bocal de farine, trop haut. Il va vers papa et dit le besoin. Un nuage blanc monte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Karim est dans la cuisine. Il veut le bocal de farine. Le bocal est en haut. Trop haut. Karim lève les bras. Il n'arrive pas. Ses épaules se tendent. Karim va vers la porte. Il va vers papa. Papa est dans le salon. Papa. J'ai besoin du bocal. Papa écoute. Papa vient. Papa donne le bocal. Le bocal est lourd. Karim dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman arrive aussi. Elle pose un saladier. Karim verse un peu de farine. Un nuage blanc monte. Papa sourit. Parce que Karim a dit le besoin, le bocal est là. Ce n'est pas être petit. C'est demander.</t>
+          <t>Le saladier de bois attend près de la vanille. La vanille sent le gâteau d'hier. Un peu de farine blanche dort sur la table. Elle est douce, comme de la neige. L'horloge fait tic, tout lentement. La fenêtre est un peu embuée. Dehors, le village est calme. Papa est dans le salon, près du canapé. Maman pose une cuillère en bois. On fait un gâteau, Aniss ? Oui. Un gâteau. En ce moment, Aniss regarde le placard. Le bocal de farine est en haut. Trop haut. Le verre du bocal brille un peu. Je veux le bocal, maman. Il est trop haut pour tes bras. Aniss lève les bras. Il n'arrive pas. Ses épaules se tendent. C'est trop difficile. Aniss va vers la porte. Il va vers papa. Papa est dans le salon. Le canapé est mou et beige. Papa. J'ai besoin du bocal. Il est trop haut. Je t'écoute, Aniss. Viens. On y va ensemble. Papa vient. Papa donne le bocal. Le bocal est lourd. Le verre est froid. Merci, papa. Bravo. Tu as dit le besoin. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman pose le saladier. Tu verses un peu de farine ? Oui, maman. Aniss verse un peu de farine. Un nuage blanc monte. Il chatouille le nez. Ça pique un peu. C'est la farine. Elle est toute légère. Parce que tu as dit le besoin, le bocal est là. Ce n'est pas être petit. C'est demander. L'horloge fait encore tic. La fenêtre est moins floue. Tu mélanges avec la cuillère ? Oui. La cuillère gratte le bois. Ça fait un bruit doux, tout rond.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,9 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Karim est dans la cuisine. Il veut le bocal de farine. Le bocal est en haut. Trop haut. Karim lève les bras. Il n'arrive pas. Ses épaules se tendent. Karim va vers la porte. Il va vers papa. Papa est dans le salon.
-enfant-m|Papa. J'ai besoin du bocal. Papa écoute. Papa vient. Papa donne le bocal.
-narrateur|Le bocal est lourd. Karim dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman arrive aussi. Elle pose un saladier. Karim verse un peu de farine. Un nuage blanc monte. Papa sourit. Parce que Karim a dit le besoin, le bocal est là. Ce n'est pas être petit. C'est demander.</t>
+          <t>narrateur|Le saladier de bois attend près de la vanille.
+narrateur|La vanille sent le gâteau d'hier.
+narrateur|Un peu de farine blanche dort sur la table.
+narrateur|Elle est douce, comme de la neige.
+narrateur|L'horloge fait tic, tout lentement.
+narrateur|La fenêtre est un peu embuée.
+narrateur|Dehors, le village est calme.
+narrateur|Papa est dans le salon, près du canapé.
+narrateur|Maman pose une cuillère en bois.
+maman|On fait un gâteau, Aniss ?
+enfant-m|Oui. Un gâteau.
+narrateur|En ce moment, Aniss regarde le placard.
+narrateur|Le bocal de farine est en haut.
+narrateur|Trop haut.
+narrateur|Le verre du bocal brille un peu.
+enfant-m|Je veux le bocal, maman.
+maman|Il est trop haut pour tes bras.
+narrateur|Aniss lève les bras.
+narrateur|Il n'arrive pas.
+narrateur|Ses épaules se tendent.
+narrateur|C'est trop difficile.
+narrateur|Aniss va vers la porte.
+narrateur|Il va vers papa.
+narrateur|Papa est dans le salon.
+narrateur|Le canapé est mou et beige.
+enfant-m|Papa. J'ai besoin du bocal.
+enfant-m|Il est trop haut.
+papa|Je t'écoute, Aniss.
+papa|Viens. On y va ensemble.
+narrateur|Papa vient.
+narrateur|Papa donne le bocal.
+narrateur|Le bocal est lourd.
+narrateur|Le verre est froid.
+enfant-m|Merci, papa.
+papa|Bravo. Tu as dit le besoin.
+maman|On peut aller vers eux.
+papa|On peut dire le besoin.
+maman|On peut appeler papa ou maman.
+narrateur|Maman pose le saladier.
+maman|Tu verses un peu de farine ?
+enfant-m|Oui, maman.
+narrateur|Aniss verse un peu de farine.
+narrateur|Un nuage blanc monte.
+narrateur|Il chatouille le nez.
+enfant-m|Ça pique un peu.
+papa|C'est la farine. Elle est toute légère.
+maman|Parce que tu as dit le besoin, le bocal est là.
+papa|Ce n'est pas être petit.
+papa|C'est demander.
+narrateur|L'horloge fait encore tic.
+narrateur|La fenêtre est moins floue.
+maman|Tu mélanges avec la cuillère ?
+enfant-m|Oui.
+narrateur|La cuillère gratte le bois.
+narrateur|Ça fait un bruit doux, tout rond.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1346,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Karim n'arrive pas. Que fait-il ?</t>
+          <t>Aniss n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,10 +1566,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Karim n'arrive pas. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Aniss n'arrive pas.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1530,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Karim a appelé. Il a dit le besoin. Papa a entendu. Le bocal est là.</t>
+          <t>Aniss a appelé. Il a dit le besoin. Papa a entendu. Le bocal est là. Tu es venu me le dire. Bravo. C'est du bon travail, Aniss. Tu as fini de verser ? Oui, maman. Un peu de farine reste sur le plan. Elle brille comme de la neige.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,10 +1734,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Karim a appelé. Il a dit le besoin. Papa a entendu. Le bocal est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a appelé.
+narrateur|Il a dit le besoin.
+narrateur|Papa a entendu.
+narrateur|Le bocal est là.
+papa|Tu es venu me le dire.
+papa|Bravo.
+maman|C'est du bon travail, Aniss.
+maman|Tu as fini de verser ?
+enfant-m|Oui, maman.
+narrateur|Un peu de farine reste sur le plan.
+narrateur|Elle brille comme de la neige.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,7 +1771,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Karim mélange la farine. Papa s'assoit près de lui.</t>
+          <t>Aniss mélange la farine. Papa s'assoit près de lui. Ça sent déjà le gâteau. Ça sent la vanille. Tu veux lécher la cuillère, après ? Oui, maman. Le saladier est lourd, maintenant. La pâte est blanche et lisse. On reste encore un peu ensemble ? Oui, papa. L'horloge fait tic. Le nuage blanc est retombé.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,10 +1907,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Karim mélange la farine. Papa s'assoit près de lui.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Aniss mélange la farine.
+narrateur|Papa s'assoit près de lui.
+papa|Ça sent déjà le gâteau.
+enfant-m|Ça sent la vanille.
+maman|Tu veux lécher la cuillère, après ?
+enfant-m|Oui, maman.
+narrateur|Le saladier est lourd, maintenant.
+narrateur|La pâte est blanche et lisse.
+papa|On reste encore un peu ensemble ?
+enfant-m|Oui, papa.
+narrateur|L'horloge fait tic.
+narrateur|Le nuage blanc est retombé.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,7 +1945,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Aniss. Tu as fait du bon travail. Le saladier n'attend plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,10 +2085,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|J'ai dit le besoin.
+papa|Oui. Tu es venu vers moi.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le saladier n'attend plus.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2149,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-05.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Karim est dans la cuisine. Il veut le bocal de farine. Le bocal est en haut. Trop haut. Karim lève les bras. Il n'arrive pas. Ses épaules se tendent. Karim va vers la porte. Il va vers papa. Papa est dans le salon. Karim dit : papa. J'ai besoin du bocal. Papa écoute. Papa vient. Papa donne le bocal. Le bocal est lourd. Karim dit merci. On peut &lt;emphasis level="moderate"&gt;aller&lt;/emphasis&gt; vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman arrive aussi. Elle pose un saladier. Karim verse un peu de farine. Un nuage blanc monte. Papa sourit. Parce que Karim a dit le besoin, le bocal est là. Ce n'est pas être petit. C'est demander.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le saladier de bois attend près de la vanille. La vanille sent le gâteau d'hier. Un peu de farine blanche dort sur la table. Elle est douce, comme de la neige. L'horloge fait tic, tout lentement. La fenêtre est un peu embuée. Dehors, le village est calme. Papa est dans le salon, près du canapé. Maman pose une cuillère en bois. On fait un gâteau, Aniss ? Oui. Un gâteau. En ce moment, Aniss regarde le placard. Le bocal de farine est en haut. Trop haut. Le verre du bocal brille un peu. Je veux le bocal, maman. Il est trop haut pour tes bras. Aniss lève les bras. Il n'arrive pas. Ses épaules se tendent. C'est trop difficile. Aniss va vers la porte. Il va vers papa. Papa est dans le salon. Le canapé est mou et beige. Papa. J'ai besoin du bocal. Il est trop haut. Je t'écoute, Aniss. Viens. On y va ensemble. Papa vient. Papa donne le bocal. Le bocal est lourd. Le verre est froid. Merci, papa. Bravo. Tu as dit le besoin. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman pose le saladier. Tu verses un peu de farine ? Oui, maman. Aniss verse un peu de farine. Un nuage blanc monte. Il chatouille le nez. Ça pique un peu. C'est la farine. Elle est toute légère. Parce que tu as dit le besoin, le bocal est là. Ce n'est pas être petit. C'est demander. L'horloge fait encore tic. La fenêtre est moins floue. Tu mélanges avec la cuillère ? Oui. La cuillère gratte le bois. Ça fait un bruit doux, tout rond.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Karim n'arrive pas. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a appelé. Il a dit le besoin. Papa a entendu. Le bocal est là. Tu es venu me le dire. Bravo. C'est du bon travail, Aniss. Tu as fini de verser ? Oui, maman. Un peu de farine reste sur le plan. Elle brille comme de la neige.</t>
+          <t>Aniss a appelé. Il a dit le besoin. Papa a entendu. Le bocal est là. Tu es venu me le dire. Bravo. Tu as fini de verser ? Oui, maman. Un peu de farine reste sur le plan. Elle brille comme de la neige.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Karim a appelé. Il a dit le besoin. Papa a entendu. Le bocal est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a appelé. Il a dit le besoin. Papa a entendu. Le bocal est là. Tu es venu me le dire. Bravo. Tu as fini de verser ? Oui, maman. Un peu de farine reste sur le plan. Elle brille comme de la neige.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1740,7 +1740,6 @@
 narrateur|Le bocal est là.
 papa|Tu es venu me le dire.
 papa|Bravo.
-maman|C'est du bon travail, Aniss.
 maman|Tu as fini de verser ?
 enfant-m|Oui, maman.
 narrateur|Un peu de farine reste sur le plan.
@@ -1776,7 +1775,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Karim mélange la farine. Papa s'assoit près de lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss mélange la farine. Papa s'assoit près de lui. Ça sent déjà le gâteau. Ça sent la vanille. Tu veux lécher la cuillère, après ? Oui, maman. Le saladier est lourd, maintenant. La pâte est blanche et lisse. On reste encore un peu ensemble ? Oui, papa. L'horloge fait tic. Le nuage blanc est retombé.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1945,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Aniss. Tu as fait du bon travail. Le saladier n'attend plus. L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Aniss. Le saladier n'attend plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Aniss. Le saladier n'attend plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2088,9 +2087,7 @@
           <t>enfant-m|J'ai dit le besoin.
 papa|Oui. Tu es venu vers moi.
 maman|Bravo, Aniss.
-maman|Tu as fait du bon travail.
-narrateur|Le saladier n'attend plus.
-narrateur|L'histoire est finie.</t>
+narrateur|Le saladier n'attend plus.</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2156,6 +2153,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-05.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karim, papa, maman</t>
+          <t>Aniss, papa, maman</t>
         </is>
       </c>
     </row>
